--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>57000</v>
+        <v>51000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1066,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45778</v>
+      </c>
+      <c r="C9" s="4">
+        <v>500</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1092,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45779</v>
+      </c>
+      <c r="C10" s="4">
+        <v>500</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1118,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45781</v>
+      </c>
+      <c r="C11" s="4">
+        <v>500</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1144,9 +1162,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45782</v>
+      </c>
+      <c r="C12" s="4">
+        <v>500</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1170,9 +1194,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45784</v>
+      </c>
+      <c r="C13" s="4">
+        <v>500</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1196,9 +1226,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45785</v>
+      </c>
+      <c r="C14" s="4">
+        <v>500</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1222,9 +1258,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45786</v>
+      </c>
+      <c r="C15" s="4">
+        <v>500</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1248,9 +1290,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45788</v>
+      </c>
+      <c r="C16" s="4">
+        <v>500</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1274,9 +1322,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45789</v>
+      </c>
+      <c r="C17" s="4">
+        <v>500</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1300,9 +1354,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45791</v>
+      </c>
+      <c r="C18" s="4">
+        <v>500</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1326,9 +1386,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45791</v>
+      </c>
+      <c r="C19" s="4">
+        <v>500</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1352,9 +1418,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45792</v>
+      </c>
+      <c r="C20" s="4">
+        <v>500</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>51000</v>
+        <v>48000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1450,9 +1450,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45793</v>
+      </c>
+      <c r="C21" s="4">
+        <v>500</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1476,9 +1482,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45794</v>
+      </c>
+      <c r="C22" s="4">
+        <v>500</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1502,9 +1514,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45795</v>
+      </c>
+      <c r="C23" s="4">
+        <v>500</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1528,9 +1546,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45797</v>
+      </c>
+      <c r="C24" s="4">
+        <v>500</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1554,9 +1578,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45799</v>
+      </c>
+      <c r="C25" s="4">
+        <v>500</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1580,9 +1610,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45803</v>
+      </c>
+      <c r="C26" s="4">
+        <v>500</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -400,7 +400,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -435,7 +435,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>48000</v>
+        <v>47500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1642,9 +1642,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45832</v>
+      </c>
+      <c r="C27" s="4">
+        <v>500</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12500</v>
+        <v>13500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>47500</v>
+        <v>46500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1674,9 +1674,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45850</v>
+      </c>
+      <c r="C28" s="4">
+        <v>500</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1700,9 +1706,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C29" s="4">
+        <v>500</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>13500</v>
+        <v>15500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>46500</v>
+        <v>44500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45861</v>
+      </c>
+      <c r="G3" s="4">
+        <v>500</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -1738,9 +1744,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45852</v>
+      </c>
+      <c r="C30" s="4">
+        <v>500</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1764,9 +1776,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45858</v>
+      </c>
+      <c r="C31" s="4">
+        <v>500</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1790,9 +1808,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45859</v>
+      </c>
+      <c r="C32" s="4">
+        <v>500</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>15500</v>
+        <v>20000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>44500</v>
+        <v>40000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -924,9 +924,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45865</v>
+      </c>
+      <c r="G4" s="4">
+        <v>500</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -956,9 +962,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45865</v>
+      </c>
+      <c r="G5" s="4">
+        <v>500</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -988,9 +1000,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45866</v>
+      </c>
+      <c r="G6" s="4">
+        <v>500</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1020,9 +1038,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45870</v>
+      </c>
+      <c r="G7" s="4">
+        <v>500</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1052,9 +1076,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45872</v>
+      </c>
+      <c r="G8" s="4">
+        <v>500</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1084,9 +1114,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45874</v>
+      </c>
+      <c r="G9" s="4">
+        <v>500</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1116,9 +1152,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45876</v>
+      </c>
+      <c r="G10" s="4">
+        <v>500</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1148,9 +1190,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45877</v>
+      </c>
+      <c r="G11" s="4">
+        <v>500</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1180,9 +1228,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45879</v>
+      </c>
+      <c r="G12" s="4">
+        <v>500</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1212,9 +1266,6 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
       <c r="I13" s="1">
         <v>71</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>20000</v>
+        <v>20500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>40000</v>
+        <v>39500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1265,6 +1265,15 @@
       </c>
       <c r="E13" s="1">
         <v>41</v>
+      </c>
+      <c r="F13" s="3">
+        <v>45886</v>
+      </c>
+      <c r="G13" s="4">
+        <v>500</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
       </c>
       <c r="I13" s="1">
         <v>71</v>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>20500</v>
+        <v>22500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>39500</v>
+        <v>37500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1304,9 +1304,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45899</v>
+      </c>
+      <c r="G14" s="4">
+        <v>500</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1336,9 +1342,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45908</v>
+      </c>
+      <c r="G15" s="4">
+        <v>500</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1368,9 +1380,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45913</v>
+      </c>
+      <c r="G16" s="4">
+        <v>500</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1400,9 +1418,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45927</v>
+      </c>
+      <c r="G17" s="4">
+        <v>500</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>22500</v>
+        <v>23500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>37500</v>
+        <v>36500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1456,9 +1456,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G18" s="4">
+        <v>500</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1488,9 +1494,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45939</v>
+      </c>
+      <c r="G19" s="4">
+        <v>500</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>23500</v>
+        <v>25500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>36500</v>
+        <v>34500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1532,9 +1532,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45942</v>
+      </c>
+      <c r="G20" s="4">
+        <v>500</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1564,9 +1570,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45946</v>
+      </c>
+      <c r="G21" s="4">
+        <v>500</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1596,9 +1608,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45947</v>
+      </c>
+      <c r="G22" s="4">
+        <v>500</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1628,9 +1646,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45949</v>
+      </c>
+      <c r="G23" s="4">
+        <v>500</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>25500</v>
+        <v>26500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>34500</v>
+        <v>33500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1684,9 +1684,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45950</v>
+      </c>
+      <c r="G24" s="4">
+        <v>500</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1716,9 +1722,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45962</v>
+      </c>
+      <c r="G25" s="4">
+        <v>500</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>26500</v>
+        <v>27000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>33500</v>
+        <v>33000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1760,9 +1760,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G26" s="4">
+        <v>500</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>33000</v>
+        <v>31500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1798,9 +1798,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>46006</v>
+      </c>
+      <c r="G27" s="4">
+        <v>500</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1830,9 +1836,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>46008</v>
+      </c>
+      <c r="G28" s="4">
+        <v>500</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1862,9 +1874,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>46009</v>
+      </c>
+      <c r="G29" s="4">
+        <v>500</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>28500</v>
+        <v>29500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>31500</v>
+        <v>30500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1912,9 +1912,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>46046</v>
+      </c>
+      <c r="G30" s="4">
+        <v>500</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1944,9 +1950,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>46046</v>
+      </c>
+      <c r="G31" s="4">
+        <v>500</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>

--- a/LoanOfficer-A/2023/106 angom bijenty.xlsx
+++ b/LoanOfficer-A/2023/106 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>29500</v>
+        <v>60000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>30500</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,15 +898,27 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>46055</v>
+      </c>
+      <c r="K3" s="4">
+        <v>500</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O3" s="4">
+        <v>500</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -936,15 +948,27 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>46060</v>
+      </c>
+      <c r="K4" s="4">
+        <v>500</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O4" s="4">
+        <v>500</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -974,15 +998,27 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>46063</v>
+      </c>
+      <c r="K5" s="4">
+        <v>500</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O5" s="4">
+        <v>500</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1012,15 +1048,27 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>46066</v>
+      </c>
+      <c r="K6" s="4">
+        <v>500</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O6" s="4">
+        <v>500</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1050,15 +1098,27 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>46067</v>
+      </c>
+      <c r="K7" s="4">
+        <v>500</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O7" s="4">
+        <v>500</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1088,15 +1148,27 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>46068</v>
+      </c>
+      <c r="K8" s="4">
+        <v>500</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O8" s="4">
+        <v>500</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1126,15 +1198,27 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>46069</v>
+      </c>
+      <c r="K9" s="4">
+        <v>500</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O9" s="4">
+        <v>500</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1164,15 +1248,27 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>46073</v>
+      </c>
+      <c r="K10" s="4">
+        <v>500</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O10" s="4">
+        <v>500</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1202,15 +1298,27 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>46073</v>
+      </c>
+      <c r="K11" s="4">
+        <v>500</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O11" s="4">
+        <v>500</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1240,15 +1348,27 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K12" s="4">
+        <v>500</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O12" s="4">
+        <v>500</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1278,15 +1398,27 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K13" s="4">
+        <v>500</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O13" s="4">
+        <v>500</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1316,15 +1448,27 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K14" s="4">
+        <v>500</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O14" s="4">
+        <v>500</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1354,15 +1498,27 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K15" s="4">
+        <v>500</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O15" s="4">
+        <v>500</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1392,15 +1548,27 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K16" s="4">
+        <v>500</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O16" s="4">
+        <v>500</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1430,15 +1598,27 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K17" s="4">
+        <v>500</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O17" s="4">
+        <v>500</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1468,15 +1648,27 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K18" s="4">
+        <v>500</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O18" s="4">
+        <v>500</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1506,15 +1698,27 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K19" s="4">
+        <v>500</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
+      <c r="N19" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O19" s="4">
+        <v>500</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1544,15 +1748,27 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K20" s="4">
+        <v>500</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
+      <c r="N20" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O20" s="4">
+        <v>500</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1582,15 +1798,27 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K21" s="4">
+        <v>500</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
+      <c r="N21" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O21" s="4">
+        <v>500</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1620,15 +1848,27 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K22" s="4">
+        <v>500</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1"/>
+      <c r="N22" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O22" s="4">
+        <v>500</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1658,15 +1898,27 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K23" s="4">
+        <v>500</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1"/>
+      <c r="N23" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O23" s="4">
+        <v>500</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1696,15 +1948,27 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K24" s="4">
+        <v>500</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1"/>
+      <c r="N24" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O24" s="4">
+        <v>500</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1734,15 +1998,27 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K25" s="4">
+        <v>500</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="1"/>
+      <c r="N25" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O25" s="4">
+        <v>500</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -1772,15 +2048,27 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K26" s="4">
+        <v>500</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1"/>
+      <c r="N26" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O26" s="4">
+        <v>500</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -1810,15 +2098,27 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K27" s="4">
+        <v>500</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="1"/>
+      <c r="N27" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O27" s="4">
+        <v>500</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -1848,15 +2148,27 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K28" s="4">
+        <v>500</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1"/>
+      <c r="N28" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O28" s="4">
+        <v>500</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -1886,15 +2198,27 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K29" s="4">
+        <v>500</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="1"/>
+      <c r="N29" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O29" s="4">
+        <v>500</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -1924,15 +2248,27 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K30" s="4">
+        <v>500</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="1"/>
+      <c r="N30" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O30" s="4">
+        <v>500</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -1962,15 +2298,27 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K31" s="4">
+        <v>500</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="1"/>
+      <c r="N31" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O31" s="4">
+        <v>500</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -1988,21 +2336,39 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>46050</v>
+      </c>
+      <c r="G32" s="4">
+        <v>500</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>46082</v>
+      </c>
+      <c r="K32" s="4">
+        <v>500</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="1"/>
+      <c r="N32" s="3">
+        <v>46082</v>
+      </c>
+      <c r="O32" s="4">
+        <v>500</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
